--- a/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_predict_faults.xlsx
+++ b/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_predict_faults.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FamiliaNatelloMedina\Desktop\codigo\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1AA372-8FB4-4C97-8B5C-FA1B5B3F9804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -159,7 +160,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -212,10 +213,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -235,9 +239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -275,9 +279,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -312,7 +316,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -347,7 +351,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -520,7 +524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Y1370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -528,7 +532,7 @@
     <col min="1" max="1" width="43.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -101111,7 +101115,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y1370">
+  <autoFilter ref="A1:Y1370" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="PRD85_PR50_CPprop_UD050_UR055_Upp045_I0"/>

--- a/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_predict_faults.xlsx
+++ b/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_predict_faults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1AA372-8FB4-4C97-8B5C-FA1B5B3F9804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A864836-7E01-483E-805E-4723E35CFD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -530,6 +530,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
